--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_35_R4.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_35_R4.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.6536</v>
+        <v>4.7459</v>
       </c>
       <c r="E2" t="n">
-        <v>3.8699</v>
+        <v>4.7269</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.2163</v>
+        <v>0.0189</v>
       </c>
       <c r="G2" t="n">
         <v>4.6488</v>
@@ -610,13 +610,13 @@
         <v>0.9278</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.9282</v>
+        <v>0.1641</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.5895</v>
+        <v>0.2675</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.3387</v>
+        <v>-0.1034</v>
       </c>
       <c r="V2" t="n">
         <v>1.3247</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.0524</v>
+        <v>2.0407</v>
       </c>
       <c r="E3" t="n">
-        <v>2.2781</v>
+        <v>1.8377</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7743</v>
+        <v>0.203</v>
       </c>
       <c r="G3" t="n">
         <v>-0.7849</v>
@@ -688,13 +688,13 @@
         <v>1.8556</v>
       </c>
       <c r="S3" t="n">
-        <v>1.9817</v>
+        <v>0.97</v>
       </c>
       <c r="T3" t="n">
-        <v>0.9911</v>
+        <v>0.5507</v>
       </c>
       <c r="U3" t="n">
-        <v>0.9906</v>
+        <v>0.4193</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.4478</v>
+        <v>1.4149</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0118</v>
+        <v>0.2477</v>
       </c>
       <c r="F4" t="n">
-        <v>1.4361</v>
+        <v>1.1672</v>
       </c>
       <c r="G4" t="n">
         <v>0.1999</v>
@@ -766,13 +766,13 @@
         <v>0.6959</v>
       </c>
       <c r="S4" t="n">
-        <v>0.4103</v>
+        <v>0.3774</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2908</v>
+        <v>-0.0549</v>
       </c>
       <c r="U4" t="n">
-        <v>0.7010999999999999</v>
+        <v>0.4323</v>
       </c>
       <c r="V4" t="n">
         <v>0.1418</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8955</v>
+        <v>0.9798</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.2149</v>
+        <v>-0.0969</v>
       </c>
       <c r="F5" t="n">
-        <v>1.1104</v>
+        <v>1.0768</v>
       </c>
       <c r="G5" t="n">
         <v>-0.002</v>
@@ -844,13 +844,13 @@
         <v>1.1598</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.2623</v>
+        <v>-0.1779</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1415</v>
+        <v>-0.0235</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1208</v>
+        <v>-0.1544</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,10 +877,10 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4228</v>
+        <v>0.7334000000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.8212</v>
+        <v>-0.5106000000000001</v>
       </c>
       <c r="F6" t="n">
         <v>1.244</v>
@@ -922,10 +922,10 @@
         <v>1.8556</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.6291</v>
+        <v>-0.3185</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.5895</v>
+        <v>-0.279</v>
       </c>
       <c r="U6" t="n">
         <v>-0.0395</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. HOARD</t>
+          <t>T. BLATT</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.3524</v>
+        <v>-1.783</v>
       </c>
       <c r="E7" t="n">
-        <v>1.9957</v>
+        <v>-0.9676</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.3482</v>
+        <v>-0.8153</v>
       </c>
       <c r="G7" t="n">
-        <v>-3.589</v>
+        <v>0.1426</v>
       </c>
       <c r="H7" t="n">
-        <v>-3.1308</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.4582</v>
+        <v>0.0668</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.1763</v>
+        <v>2.0516</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.2499</v>
+        <v>1.6637</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0736</v>
+        <v>0.3879</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.4127</v>
+        <v>-1.909</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.8809</v>
+        <v>-1.5879</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.5319</v>
+        <v>-0.3211</v>
       </c>
       <c r="P7" t="n">
-        <v>0.9278</v>
+        <v>-3.9432</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-5.7988</v>
       </c>
       <c r="R7" t="n">
-        <v>0.9278</v>
+        <v>1.8556</v>
       </c>
       <c r="S7" t="n">
-        <v>1.2366</v>
+        <v>-0.9465</v>
       </c>
       <c r="T7" t="n">
-        <v>2.0998</v>
+        <v>-0.1845</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.8632</v>
+        <v>-0.762</v>
       </c>
       <c r="V7" t="n">
-        <v>1.0722</v>
+        <v>2.9641</v>
       </c>
       <c r="W7" t="n">
-        <v>1.0722</v>
+        <v>2.9641</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>T. BLATT</t>
+          <t>J. DOWTIN JR</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.6319</v>
+        <v>-1.8524</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.5141</v>
+        <v>-1.1126</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.1178</v>
+        <v>-0.7398</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1426</v>
+        <v>-1.1694</v>
       </c>
       <c r="H8" t="n">
-        <v>0.07580000000000001</v>
+        <v>-2.2401</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0668</v>
+        <v>1.0707</v>
       </c>
       <c r="J8" t="n">
-        <v>2.0516</v>
+        <v>-1.1442</v>
       </c>
       <c r="K8" t="n">
-        <v>1.6637</v>
+        <v>-1.5356</v>
       </c>
       <c r="L8" t="n">
-        <v>0.3879</v>
+        <v>0.3914</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.909</v>
+        <v>-0.0252</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.5879</v>
+        <v>-0.7045</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.3211</v>
+        <v>0.6793</v>
       </c>
       <c r="P8" t="n">
-        <v>-3.9432</v>
+        <v>0.4639</v>
       </c>
       <c r="Q8" t="n">
-        <v>-5.7988</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.8556</v>
+        <v>0.4639</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.7954</v>
+        <v>-0.0747</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.731</v>
+        <v>0.0316</v>
       </c>
       <c r="U8" t="n">
-        <v>-1.0644</v>
+        <v>-0.1063</v>
       </c>
       <c r="V8" t="n">
-        <v>2.9641</v>
+        <v>-1.0722</v>
       </c>
       <c r="W8" t="n">
-        <v>2.9641</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. DOWTIN JR</t>
+          <t>J. HOARD</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.6677</v>
+        <v>-2.0224</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.659</v>
+        <v>0.4938</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.0087</v>
+        <v>-2.5162</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.1694</v>
+        <v>-3.589</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.2401</v>
+        <v>-3.1308</v>
       </c>
       <c r="I9" t="n">
-        <v>1.0707</v>
+        <v>-0.4582</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.1442</v>
+        <v>-1.1763</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.5356</v>
+        <v>-1.2499</v>
       </c>
       <c r="L9" t="n">
-        <v>0.3914</v>
+        <v>0.0736</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.0252</v>
+        <v>-2.4127</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.7045</v>
+        <v>-1.8809</v>
       </c>
       <c r="O9" t="n">
-        <v>0.6793</v>
+        <v>-0.5319</v>
       </c>
       <c r="P9" t="n">
-        <v>0.4639</v>
+        <v>0.9278</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.4639</v>
+        <v>0.9278</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.89</v>
+        <v>-0.4334</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5149</v>
+        <v>0.5979</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3752</v>
+        <v>-1.0313</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.0722</v>
+        <v>1.0722</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>R. SORKIN</t>
+          <t>J. CLARK III</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,64 +1189,64 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.5134</v>
+        <v>-3.5042</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.1902</v>
+        <v>-2.4818</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.3232</v>
+        <v>-1.0224</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.2399</v>
+        <v>-2.3755</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.718</v>
+        <v>-0.234</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.5219</v>
+        <v>-2.1415</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.0703</v>
+        <v>-1.4677</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.4985</v>
+        <v>0.3025</v>
       </c>
       <c r="L10" t="n">
-        <v>0.4282</v>
+        <v>-1.7702</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.1696</v>
+        <v>-0.9078000000000001</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.2195</v>
+        <v>-0.5365</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.9500999999999999</v>
+        <v>-0.3713</v>
       </c>
       <c r="P10" t="n">
-        <v>0.6959</v>
+        <v>-0.232</v>
       </c>
       <c r="Q10" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R10" t="n">
-        <v>1.8556</v>
+        <v>0.9278</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.575</v>
+        <v>-0.3607</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1019</v>
+        <v>0.1456</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4731</v>
+        <v>-0.5063</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.3943</v>
+        <v>-0.5361</v>
       </c>
       <c r="W10" t="n">
-        <v>0.1418</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
         <v>-0.5361</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. CLARK III</t>
+          <t>R. SORKIN</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,64 +1267,64 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.629</v>
+        <v>-3.759</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.4385</v>
+        <v>-2.4693</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.1904</v>
+        <v>-1.2896</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.3755</v>
+        <v>-3.2399</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.234</v>
+        <v>-2.718</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.1415</v>
+        <v>-0.5219</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.4677</v>
+        <v>-1.0703</v>
       </c>
       <c r="K11" t="n">
-        <v>0.3025</v>
+        <v>-1.4985</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.7702</v>
+        <v>0.4282</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.9078000000000001</v>
+        <v>-2.1696</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.5365</v>
+        <v>-1.2195</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.3713</v>
+        <v>-0.9500999999999999</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.232</v>
+        <v>0.6959</v>
       </c>
       <c r="Q11" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R11" t="n">
-        <v>0.9278</v>
+        <v>1.8556</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.4854</v>
+        <v>-0.8206</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1889</v>
+        <v>-0.3811</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.6743</v>
+        <v>-0.4395</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.5361</v>
+        <v>-0.3943</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>0.1418</v>
       </c>
       <c r="X11" t="n">
         <v>-0.5361</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.5704</v>
+        <v>-4.2524</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.4571</v>
+        <v>-1.0719</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.1133</v>
+        <v>-3.1805</v>
       </c>
       <c r="G12" t="n">
         <v>-3.8943</v>
@@ -1390,13 +1390,13 @@
         <v>0.6959</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.5834</v>
+        <v>-0.2653</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.2592</v>
+        <v>0.1261</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.3242</v>
+        <v>-0.3914</v>
       </c>
       <c r="V12" t="n">
         <v>-0.7886</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-9.3497</v>
+        <v>-8.8636</v>
       </c>
       <c r="E13" t="n">
-        <v>-6.6792</v>
+        <v>-6.2939</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.6705</v>
+        <v>-2.5697</v>
       </c>
       <c r="G13" t="n">
         <v>-4.5746</v>
@@ -1468,13 +1468,13 @@
         <v>0.6959</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.9195</v>
+        <v>-0.4334</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.3339</v>
+        <v>0.0514</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.5856</v>
+        <v>-0.4848</v>
       </c>
       <c r="V13" t="n">
         <v>-1.0722</v>
@@ -1501,10 +1501,10 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-17.2424</v>
+        <v>-16.1223</v>
       </c>
       <c r="E14" t="n">
-        <v>-8.8187</v>
+        <v>-7.6985</v>
       </c>
       <c r="F14" t="n">
         <v>-8.4236</v>
@@ -1522,7 +1522,7 @@
         <v>-3.6632</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.8181</v>
+        <v>-0.8180999999999998</v>
       </c>
       <c r="L14" t="n">
         <v>-2.8453</v>
@@ -1531,13 +1531,13 @@
         <v>-11.7788</v>
       </c>
       <c r="N14" t="n">
-        <v>-9.889700000000001</v>
+        <v>-9.889699999999999</v>
       </c>
       <c r="O14" t="n">
         <v>-1.8894</v>
       </c>
       <c r="P14" t="n">
-        <v>9.999999999932285e-05</v>
+        <v>9.999999999976694e-05</v>
       </c>
       <c r="Q14" t="n">
         <v>-13.9172</v>
@@ -1546,10 +1546,10 @@
         <v>13.9172</v>
       </c>
       <c r="S14" t="n">
-        <v>-3.4397</v>
+        <v>-2.319500000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.2724</v>
+        <v>0.8477999999999999</v>
       </c>
       <c r="U14" t="n">
         <v>-3.1673</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>8.1633</v>
+        <v>6.9508</v>
       </c>
       <c r="E15" t="n">
-        <v>5.2077</v>
+        <v>4.2641</v>
       </c>
       <c r="F15" t="n">
-        <v>2.9556</v>
+        <v>2.6867</v>
       </c>
       <c r="G15" t="n">
         <v>4.2655</v>
@@ -1624,13 +1624,13 @@
         <v>1.1598</v>
       </c>
       <c r="S15" t="n">
-        <v>2.5963</v>
+        <v>1.3838</v>
       </c>
       <c r="T15" t="n">
-        <v>1.9189</v>
+        <v>0.9752</v>
       </c>
       <c r="U15" t="n">
-        <v>0.6774</v>
+        <v>0.4086</v>
       </c>
       <c r="V15" t="n">
         <v>0.1418</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>6.6286</v>
+        <v>5.2367</v>
       </c>
       <c r="E16" t="n">
-        <v>6.2523</v>
+        <v>5.0728</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3763</v>
+        <v>0.1639</v>
       </c>
       <c r="G16" t="n">
         <v>3.7311</v>
@@ -1702,13 +1702,13 @@
         <v>1.3917</v>
       </c>
       <c r="S16" t="n">
-        <v>2.7531</v>
+        <v>1.3612</v>
       </c>
       <c r="T16" t="n">
-        <v>2.0603</v>
+        <v>0.8808</v>
       </c>
       <c r="U16" t="n">
-        <v>0.6928</v>
+        <v>0.4804</v>
       </c>
       <c r="V16" t="n">
         <v>1.0722</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>4.0764</v>
+        <v>5.0359</v>
       </c>
       <c r="E17" t="n">
-        <v>2.3888</v>
+        <v>2.9786</v>
       </c>
       <c r="F17" t="n">
-        <v>1.6876</v>
+        <v>2.0573</v>
       </c>
       <c r="G17" t="n">
         <v>5.7657</v>
@@ -1780,13 +1780,13 @@
         <v>0.9278</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.9212</v>
+        <v>0.0382</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.2908</v>
+        <v>0.2989</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.6304</v>
+        <v>-0.2607</v>
       </c>
       <c r="V17" t="n">
         <v>-0.5361</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>3.8532</v>
+        <v>3.1962</v>
       </c>
       <c r="E18" t="n">
-        <v>1.1932</v>
+        <v>0.6034</v>
       </c>
       <c r="F18" t="n">
-        <v>2.66</v>
+        <v>2.5928</v>
       </c>
       <c r="G18" t="n">
         <v>0.9417</v>
@@ -1858,13 +1858,13 @@
         <v>1.1598</v>
       </c>
       <c r="S18" t="n">
-        <v>1.5867</v>
+        <v>0.9298</v>
       </c>
       <c r="T18" t="n">
-        <v>1.2072</v>
+        <v>0.6173999999999999</v>
       </c>
       <c r="U18" t="n">
-        <v>0.3796</v>
+        <v>0.3123</v>
       </c>
       <c r="V18" t="n">
         <v>1.3247</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>2.0065</v>
+        <v>2.7307</v>
       </c>
       <c r="E19" t="n">
-        <v>0.1422</v>
+        <v>0.7319</v>
       </c>
       <c r="F19" t="n">
-        <v>1.8643</v>
+        <v>1.9988</v>
       </c>
       <c r="G19" t="n">
         <v>-1.3047</v>
@@ -1936,13 +1936,13 @@
         <v>1.3917</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.2249</v>
+        <v>0.4993</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3655</v>
+        <v>0.2243</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1406</v>
+        <v>0.275</v>
       </c>
       <c r="V19" t="n">
         <v>2.1444</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.1803</v>
+        <v>2.4714</v>
       </c>
       <c r="E20" t="n">
-        <v>1.5103</v>
+        <v>2.218</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.33</v>
+        <v>0.2534</v>
       </c>
       <c r="G20" t="n">
         <v>2.8286</v>
@@ -2014,13 +2014,13 @@
         <v>1.3917</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.6843</v>
+        <v>-0.3932</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.8962</v>
+        <v>-0.1885</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.7881</v>
+        <v>-0.2047</v>
       </c>
       <c r="V20" t="n">
         <v>-1.3558</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.1626</v>
+        <v>1.6167</v>
       </c>
       <c r="E21" t="n">
-        <v>0.0423</v>
+        <v>1.1038</v>
       </c>
       <c r="F21" t="n">
-        <v>0.1204</v>
+        <v>0.5129</v>
       </c>
       <c r="G21" t="n">
         <v>1.3383</v>
@@ -2092,13 +2092,13 @@
         <v>1.3917</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.5494</v>
+        <v>-0.0953</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.8962</v>
+        <v>0.1654</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.6532</v>
+        <v>-0.2607</v>
       </c>
       <c r="V21" t="n">
         <v>0.1418</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>M. NORRIS</t>
+          <t>S. KEITA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.7934</v>
+        <v>-0.8969</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.1553</v>
+        <v>-0.538</v>
       </c>
       <c r="F22" t="n">
-        <v>1.3619</v>
+        <v>-0.3589</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.8234</v>
+        <v>1.1502</v>
       </c>
       <c r="H22" t="n">
-        <v>1.1909</v>
+        <v>-0.2017</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.0143</v>
+        <v>1.3519</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.4377</v>
+        <v>0.5036</v>
       </c>
       <c r="K22" t="n">
-        <v>0.9411</v>
+        <v>0.3564</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.3787</v>
+        <v>0.1472</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.3858</v>
+        <v>0.6466</v>
       </c>
       <c r="N22" t="n">
-        <v>0.2499</v>
+        <v>-0.5581</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.6356000000000001</v>
+        <v>1.2046</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.6959</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.3195</v>
+        <v>-1.1598</v>
       </c>
       <c r="R22" t="n">
-        <v>1.6237</v>
+        <v>1.1598</v>
       </c>
       <c r="S22" t="n">
-        <v>0.8676</v>
+        <v>0.0973</v>
       </c>
       <c r="T22" t="n">
-        <v>0.6018</v>
+        <v>0.1182</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2658</v>
+        <v>-0.0209</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.1418</v>
+        <v>-2.1444</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.1418</v>
+        <v>-2.1444</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>J. PARRA</t>
+          <t>M. NORRIS</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,64 +2203,64 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.3435</v>
+        <v>-1.2532</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.0075</v>
+        <v>-2.6271</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.336</v>
+        <v>1.374</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.9846</v>
+        <v>-0.8234</v>
       </c>
       <c r="H23" t="n">
-        <v>0.3973</v>
+        <v>1.1909</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.3819</v>
+        <v>-2.0143</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.4772</v>
+        <v>-0.4377</v>
       </c>
       <c r="K23" t="n">
-        <v>0.2724</v>
+        <v>0.9411</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.7495000000000001</v>
+        <v>-1.3787</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.5074</v>
+        <v>-0.3858</v>
       </c>
       <c r="N23" t="n">
-        <v>0.1249</v>
+        <v>0.2499</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.6323</v>
+        <v>-0.6356000000000001</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.9278</v>
+        <v>-0.6959</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.1598</v>
+        <v>-2.3195</v>
       </c>
       <c r="R23" t="n">
-        <v>0.232</v>
+        <v>1.6237</v>
       </c>
       <c r="S23" t="n">
-        <v>0.5689</v>
+        <v>0.4079</v>
       </c>
       <c r="T23" t="n">
-        <v>0.4876</v>
+        <v>0.13</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0813</v>
+        <v>0.2779</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>-0.1418</v>
       </c>
       <c r="W23" t="n">
-        <v>0.1418</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
         <v>-0.1418</v>
@@ -2269,7 +2269,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>S. KEITA</t>
+          <t>J. PARRA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.571</v>
+        <v>-1.3885</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.2457</v>
+        <v>-1.2434</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.3253</v>
+        <v>-0.1451</v>
       </c>
       <c r="G24" t="n">
-        <v>1.1502</v>
+        <v>-0.9846</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.2017</v>
+        <v>0.3973</v>
       </c>
       <c r="I24" t="n">
-        <v>1.3519</v>
+        <v>-1.3819</v>
       </c>
       <c r="J24" t="n">
-        <v>0.5036</v>
+        <v>-0.4772</v>
       </c>
       <c r="K24" t="n">
-        <v>0.3564</v>
+        <v>0.2724</v>
       </c>
       <c r="L24" t="n">
-        <v>0.1472</v>
+        <v>-0.7495000000000001</v>
       </c>
       <c r="M24" t="n">
-        <v>0.6466</v>
+        <v>-0.5074</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.5581</v>
+        <v>0.1249</v>
       </c>
       <c r="O24" t="n">
-        <v>1.2046</v>
+        <v>-0.6323</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>-0.9278</v>
       </c>
       <c r="Q24" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R24" t="n">
-        <v>1.1598</v>
+        <v>0.232</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.5768</v>
+        <v>0.5239</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.5895</v>
+        <v>0.2517</v>
       </c>
       <c r="U24" t="n">
-        <v>0.0127</v>
+        <v>0.2721</v>
       </c>
       <c r="V24" t="n">
-        <v>-2.1444</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>0.1418</v>
       </c>
       <c r="X24" t="n">
-        <v>-2.1444</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="25">
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-2.4841</v>
+        <v>-2.0909</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.8061</v>
+        <v>-1.5702</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.678</v>
+        <v>-0.5207000000000001</v>
       </c>
       <c r="G25" t="n">
         <v>0.0624</v>
@@ -2404,13 +2404,13 @@
         <v>0.232</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.5465</v>
+        <v>-0.1533</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.5228</v>
+        <v>-0.2869</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.0237</v>
+        <v>0.1336</v>
       </c>
       <c r="V25" t="n">
         <v>-1.0722</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-2.6364</v>
+        <v>-2.7937</v>
       </c>
       <c r="E26" t="n">
-        <v>-2.0984</v>
+        <v>-2.5702</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.5381</v>
+        <v>-0.2235</v>
       </c>
       <c r="G26" t="n">
         <v>-1.5287</v>
@@ -2482,13 +2482,13 @@
         <v>1.8556</v>
       </c>
       <c r="S26" t="n">
-        <v>0.5702</v>
+        <v>0.4129</v>
       </c>
       <c r="T26" t="n">
-        <v>0.4525</v>
+        <v>-0.0193</v>
       </c>
       <c r="U26" t="n">
-        <v>0.1177</v>
+        <v>0.4323</v>
       </c>
       <c r="V26" t="n">
         <v>-1.214</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>17.2425</v>
+        <v>18.8152</v>
       </c>
       <c r="E27" t="n">
-        <v>8.423800000000002</v>
+        <v>8.4237</v>
       </c>
       <c r="F27" t="n">
-        <v>8.8187</v>
+        <v>10.3916</v>
       </c>
       <c r="G27" t="n">
         <v>15.4421</v>
@@ -2551,7 +2551,7 @@
         <v>2.8451</v>
       </c>
       <c r="P27" t="n">
-        <v>-2.220446049250313e-16</v>
+        <v>2.220446049250313e-16</v>
       </c>
       <c r="Q27" t="n">
         <v>-13.9173</v>
@@ -2560,13 +2560,13 @@
         <v>13.9173</v>
       </c>
       <c r="S27" t="n">
-        <v>3.439699999999999</v>
+        <v>5.0125</v>
       </c>
       <c r="T27" t="n">
-        <v>3.1673</v>
+        <v>3.167199999999999</v>
       </c>
       <c r="U27" t="n">
-        <v>0.2725000000000002</v>
+        <v>1.8452</v>
       </c>
       <c r="V27" t="n">
         <v>-1.6394</v>
